--- a/daily_generation_file.xlsx
+++ b/daily_generation_file.xlsx
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1119"/>
+  <dimension ref="A1:M1138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -45945,6 +45945,785 @@
         <v>221575</v>
       </c>
     </row>
+    <row r="1120" spans="1:13">
+      <c r="A1120" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B1120">
+        <v>4953.08</v>
+      </c>
+      <c r="C1120">
+        <v>0.058</v>
+      </c>
+      <c r="D1120">
+        <v>4953.138</v>
+      </c>
+      <c r="E1120">
+        <v>215960</v>
+      </c>
+      <c r="F1120">
+        <v>223</v>
+      </c>
+      <c r="G1120">
+        <v>216183</v>
+      </c>
+      <c r="H1120">
+        <v>217814</v>
+      </c>
+      <c r="I1120">
+        <v>0</v>
+      </c>
+      <c r="J1120">
+        <v>217814</v>
+      </c>
+      <c r="K1120">
+        <v>218120</v>
+      </c>
+      <c r="L1120">
+        <v>0</v>
+      </c>
+      <c r="M1120">
+        <v>218120</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:13">
+      <c r="A1121" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B1121">
+        <v>5014.58</v>
+      </c>
+      <c r="C1121">
+        <v>0.244</v>
+      </c>
+      <c r="D1121">
+        <v>5014.824</v>
+      </c>
+      <c r="E1121">
+        <v>218418</v>
+      </c>
+      <c r="F1121">
+        <v>0</v>
+      </c>
+      <c r="G1121">
+        <v>218418</v>
+      </c>
+      <c r="H1121">
+        <v>223878</v>
+      </c>
+      <c r="I1121">
+        <v>0</v>
+      </c>
+      <c r="J1121">
+        <v>223878</v>
+      </c>
+      <c r="K1121">
+        <v>221314</v>
+      </c>
+      <c r="L1121">
+        <v>0</v>
+      </c>
+      <c r="M1121">
+        <v>221314</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:13">
+      <c r="A1122" s="2">
+        <v>46151</v>
+      </c>
+      <c r="B1122">
+        <v>5045.55</v>
+      </c>
+      <c r="C1122">
+        <v>0</v>
+      </c>
+      <c r="D1122">
+        <v>5045.55</v>
+      </c>
+      <c r="E1122">
+        <v>218947</v>
+      </c>
+      <c r="F1122">
+        <v>100</v>
+      </c>
+      <c r="G1122">
+        <v>219047</v>
+      </c>
+      <c r="H1122">
+        <v>226682</v>
+      </c>
+      <c r="I1122">
+        <v>0</v>
+      </c>
+      <c r="J1122">
+        <v>226682</v>
+      </c>
+      <c r="K1122">
+        <v>223016</v>
+      </c>
+      <c r="L1122">
+        <v>80</v>
+      </c>
+      <c r="M1122">
+        <v>223096</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:13">
+      <c r="A1123" s="2">
+        <v>46152</v>
+      </c>
+      <c r="B1123">
+        <v>4955.54</v>
+      </c>
+      <c r="C1123">
+        <v>0.128</v>
+      </c>
+      <c r="D1123">
+        <v>4955.668</v>
+      </c>
+      <c r="E1123">
+        <v>218416</v>
+      </c>
+      <c r="F1123">
+        <v>173</v>
+      </c>
+      <c r="G1123">
+        <v>218589</v>
+      </c>
+      <c r="H1123">
+        <v>212671</v>
+      </c>
+      <c r="I1123">
+        <v>0</v>
+      </c>
+      <c r="J1123">
+        <v>212671</v>
+      </c>
+      <c r="K1123">
+        <v>224820</v>
+      </c>
+      <c r="L1123">
+        <v>0</v>
+      </c>
+      <c r="M1123">
+        <v>224820</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:13">
+      <c r="A1124" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B1124">
+        <v>5270.72</v>
+      </c>
+      <c r="C1124">
+        <v>12.193</v>
+      </c>
+      <c r="D1124">
+        <v>5282.913</v>
+      </c>
+      <c r="E1124">
+        <v>230500</v>
+      </c>
+      <c r="F1124">
+        <v>2329</v>
+      </c>
+      <c r="G1124">
+        <v>232829</v>
+      </c>
+      <c r="H1124">
+        <v>241522</v>
+      </c>
+      <c r="I1124">
+        <v>0</v>
+      </c>
+      <c r="J1124">
+        <v>241522</v>
+      </c>
+      <c r="K1124">
+        <v>234304</v>
+      </c>
+      <c r="L1124">
+        <v>2692</v>
+      </c>
+      <c r="M1124">
+        <v>236996</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:13">
+      <c r="A1125" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B1125">
+        <v>5456.67</v>
+      </c>
+      <c r="C1125">
+        <v>10.29</v>
+      </c>
+      <c r="D1125">
+        <v>5466.96</v>
+      </c>
+      <c r="E1125">
+        <v>234506</v>
+      </c>
+      <c r="F1125">
+        <v>1185</v>
+      </c>
+      <c r="G1125">
+        <v>235691</v>
+      </c>
+      <c r="H1125">
+        <v>247881</v>
+      </c>
+      <c r="I1125">
+        <v>0</v>
+      </c>
+      <c r="J1125">
+        <v>247881</v>
+      </c>
+      <c r="K1125">
+        <v>238289</v>
+      </c>
+      <c r="L1125">
+        <v>2248</v>
+      </c>
+      <c r="M1125">
+        <v>240537</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:13">
+      <c r="A1126" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B1126">
+        <v>5418.55</v>
+      </c>
+      <c r="C1126">
+        <v>2.8</v>
+      </c>
+      <c r="D1126">
+        <v>5421.35</v>
+      </c>
+      <c r="E1126">
+        <v>218243</v>
+      </c>
+      <c r="F1126">
+        <v>0</v>
+      </c>
+      <c r="G1126">
+        <v>218243</v>
+      </c>
+      <c r="H1126">
+        <v>247680</v>
+      </c>
+      <c r="I1126">
+        <v>85</v>
+      </c>
+      <c r="J1126">
+        <v>247765</v>
+      </c>
+      <c r="K1126">
+        <v>232877</v>
+      </c>
+      <c r="L1126">
+        <v>800</v>
+      </c>
+      <c r="M1126">
+        <v>233677</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:13">
+      <c r="A1127" s="2">
+        <v>46156</v>
+      </c>
+      <c r="B1127">
+        <v>5360.83</v>
+      </c>
+      <c r="C1127">
+        <v>0.33</v>
+      </c>
+      <c r="D1127">
+        <v>5361.16</v>
+      </c>
+      <c r="E1127">
+        <v>234354</v>
+      </c>
+      <c r="F1127">
+        <v>330</v>
+      </c>
+      <c r="G1127">
+        <v>234684</v>
+      </c>
+      <c r="H1127">
+        <v>250296</v>
+      </c>
+      <c r="I1127">
+        <v>0</v>
+      </c>
+      <c r="J1127">
+        <v>250296</v>
+      </c>
+      <c r="K1127">
+        <v>238353</v>
+      </c>
+      <c r="L1127">
+        <v>0</v>
+      </c>
+      <c r="M1127">
+        <v>238353</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:13">
+      <c r="A1128" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B1128">
+        <v>5422.51</v>
+      </c>
+      <c r="C1128">
+        <v>1.603</v>
+      </c>
+      <c r="D1128">
+        <v>5424.113</v>
+      </c>
+      <c r="E1128">
+        <v>234019</v>
+      </c>
+      <c r="F1128">
+        <v>255</v>
+      </c>
+      <c r="G1128">
+        <v>234274</v>
+      </c>
+      <c r="H1128">
+        <v>247403</v>
+      </c>
+      <c r="I1128">
+        <v>0</v>
+      </c>
+      <c r="J1128">
+        <v>247403</v>
+      </c>
+      <c r="K1128">
+        <v>239934</v>
+      </c>
+      <c r="L1128">
+        <v>0</v>
+      </c>
+      <c r="M1128">
+        <v>239934</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:13">
+      <c r="A1129" s="2">
+        <v>46158</v>
+      </c>
+      <c r="B1129">
+        <v>5467.27</v>
+      </c>
+      <c r="C1129">
+        <v>2.984</v>
+      </c>
+      <c r="D1129">
+        <v>5470.254000000001</v>
+      </c>
+      <c r="E1129">
+        <v>234576</v>
+      </c>
+      <c r="F1129">
+        <v>200</v>
+      </c>
+      <c r="G1129">
+        <v>234776</v>
+      </c>
+      <c r="H1129">
+        <v>248681</v>
+      </c>
+      <c r="I1129">
+        <v>0</v>
+      </c>
+      <c r="J1129">
+        <v>248681</v>
+      </c>
+      <c r="K1129">
+        <v>240653</v>
+      </c>
+      <c r="L1129">
+        <v>796</v>
+      </c>
+      <c r="M1129">
+        <v>241449</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:13">
+      <c r="A1130" s="2">
+        <v>46159</v>
+      </c>
+      <c r="B1130">
+        <v>5332.12</v>
+      </c>
+      <c r="C1130">
+        <v>3.299</v>
+      </c>
+      <c r="D1130">
+        <v>5335.419</v>
+      </c>
+      <c r="E1130">
+        <v>229166</v>
+      </c>
+      <c r="F1130">
+        <v>0</v>
+      </c>
+      <c r="G1130">
+        <v>229166</v>
+      </c>
+      <c r="H1130">
+        <v>232501</v>
+      </c>
+      <c r="I1130">
+        <v>0</v>
+      </c>
+      <c r="J1130">
+        <v>232501</v>
+      </c>
+      <c r="K1130">
+        <v>238406</v>
+      </c>
+      <c r="L1130">
+        <v>400</v>
+      </c>
+      <c r="M1130">
+        <v>238806</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:13">
+      <c r="A1131" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B1131">
+        <v>5615.02</v>
+      </c>
+      <c r="C1131">
+        <v>4.541</v>
+      </c>
+      <c r="D1131">
+        <v>5619.561000000001</v>
+      </c>
+      <c r="E1131">
+        <v>241237</v>
+      </c>
+      <c r="F1131">
+        <v>601</v>
+      </c>
+      <c r="G1131">
+        <v>241838</v>
+      </c>
+      <c r="H1131">
+        <v>257370</v>
+      </c>
+      <c r="I1131">
+        <v>0</v>
+      </c>
+      <c r="J1131">
+        <v>257370</v>
+      </c>
+      <c r="K1131">
+        <v>247211</v>
+      </c>
+      <c r="L1131">
+        <v>1317</v>
+      </c>
+      <c r="M1131">
+        <v>248528</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:13">
+      <c r="A1132" s="2">
+        <v>46161</v>
+      </c>
+      <c r="B1132">
+        <v>5717.44</v>
+      </c>
+      <c r="C1132">
+        <v>4.913</v>
+      </c>
+      <c r="D1132">
+        <v>5722.352999999999</v>
+      </c>
+      <c r="E1132">
+        <v>244904</v>
+      </c>
+      <c r="F1132">
+        <v>341</v>
+      </c>
+      <c r="G1132">
+        <v>245245</v>
+      </c>
+      <c r="H1132">
+        <v>260457</v>
+      </c>
+      <c r="I1132">
+        <v>0</v>
+      </c>
+      <c r="J1132">
+        <v>260457</v>
+      </c>
+      <c r="K1132">
+        <v>251544</v>
+      </c>
+      <c r="L1132">
+        <v>698</v>
+      </c>
+      <c r="M1132">
+        <v>252242</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:13">
+      <c r="A1133" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1133">
+        <v>5802.63</v>
+      </c>
+      <c r="C1133">
+        <v>7.75232</v>
+      </c>
+      <c r="D1133">
+        <v>5810.38232</v>
+      </c>
+      <c r="E1133">
+        <v>246170</v>
+      </c>
+      <c r="F1133">
+        <v>175</v>
+      </c>
+      <c r="G1133">
+        <v>246345</v>
+      </c>
+      <c r="H1133">
+        <v>265440</v>
+      </c>
+      <c r="I1133">
+        <v>0</v>
+      </c>
+      <c r="J1133">
+        <v>265440</v>
+      </c>
+      <c r="K1133">
+        <v>251930</v>
+      </c>
+      <c r="L1133">
+        <v>1662</v>
+      </c>
+      <c r="M1133">
+        <v>253592</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:13">
+      <c r="A1134" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1134">
+        <v>5830.35</v>
+      </c>
+      <c r="C1134">
+        <v>15.01826</v>
+      </c>
+      <c r="D1134">
+        <v>5845.36826</v>
+      </c>
+      <c r="E1134">
+        <v>246091</v>
+      </c>
+      <c r="F1134">
+        <v>1695</v>
+      </c>
+      <c r="G1134">
+        <v>247786</v>
+      </c>
+      <c r="H1134">
+        <v>270820</v>
+      </c>
+      <c r="I1134">
+        <v>188</v>
+      </c>
+      <c r="J1134">
+        <v>271008</v>
+      </c>
+      <c r="K1134">
+        <v>251964</v>
+      </c>
+      <c r="L1134">
+        <v>2574</v>
+      </c>
+      <c r="M1134">
+        <v>254538</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:13">
+      <c r="A1135" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B1135">
+        <v>5820.93</v>
+      </c>
+      <c r="C1135">
+        <v>7.62</v>
+      </c>
+      <c r="D1135">
+        <v>5828.55</v>
+      </c>
+      <c r="E1135">
+        <v>244594</v>
+      </c>
+      <c r="F1135">
+        <v>300</v>
+      </c>
+      <c r="G1135">
+        <v>244894</v>
+      </c>
+      <c r="H1135">
+        <v>267680</v>
+      </c>
+      <c r="I1135">
+        <v>234</v>
+      </c>
+      <c r="J1135">
+        <v>267914</v>
+      </c>
+      <c r="K1135">
+        <v>253294</v>
+      </c>
+      <c r="L1135">
+        <v>1118</v>
+      </c>
+      <c r="M1135">
+        <v>254412</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:13">
+      <c r="A1136" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B1136">
+        <v>5755.94</v>
+      </c>
+      <c r="C1136">
+        <v>7.3716</v>
+      </c>
+      <c r="D1136">
+        <v>5763.3116</v>
+      </c>
+      <c r="E1136">
+        <v>244111</v>
+      </c>
+      <c r="F1136">
+        <v>300</v>
+      </c>
+      <c r="G1136">
+        <v>244411</v>
+      </c>
+      <c r="H1136">
+        <v>259812</v>
+      </c>
+      <c r="I1136">
+        <v>0</v>
+      </c>
+      <c r="J1136">
+        <v>259812</v>
+      </c>
+      <c r="K1136">
+        <v>248605</v>
+      </c>
+      <c r="L1136">
+        <v>1438</v>
+      </c>
+      <c r="M1136">
+        <v>250043</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:13">
+      <c r="A1137" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B1137">
+        <v>5513.17</v>
+      </c>
+      <c r="C1137">
+        <v>3.48</v>
+      </c>
+      <c r="D1137">
+        <v>5516.65</v>
+      </c>
+      <c r="E1137">
+        <v>235363</v>
+      </c>
+      <c r="F1137">
+        <v>131</v>
+      </c>
+      <c r="G1137">
+        <v>235494</v>
+      </c>
+      <c r="H1137">
+        <v>243726</v>
+      </c>
+      <c r="I1137">
+        <v>0</v>
+      </c>
+      <c r="J1137">
+        <v>243726</v>
+      </c>
+      <c r="K1137">
+        <v>247975</v>
+      </c>
+      <c r="L1137">
+        <v>456</v>
+      </c>
+      <c r="M1137">
+        <v>248431</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:13">
+      <c r="A1138" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B1138">
+        <v>5755.23</v>
+      </c>
+      <c r="C1138">
+        <v>11.24</v>
+      </c>
+      <c r="D1138">
+        <v>5766.469999999999</v>
+      </c>
+      <c r="E1138">
+        <v>242190</v>
+      </c>
+      <c r="F1138">
+        <v>1100</v>
+      </c>
+      <c r="G1138">
+        <v>243290</v>
+      </c>
+      <c r="H1138">
+        <v>268096</v>
+      </c>
+      <c r="I1138">
+        <v>0</v>
+      </c>
+      <c r="J1138">
+        <v>268096</v>
+      </c>
+      <c r="K1138">
+        <v>248516</v>
+      </c>
+      <c r="L1138">
+        <v>2768</v>
+      </c>
+      <c r="M1138">
+        <v>251284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/daily_generation_file.xlsx
+++ b/daily_generation_file.xlsx
@@ -414,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1138"/>
+  <dimension ref="A1:M1151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -46724,6 +46724,413 @@
         <v>251284</v>
       </c>
     </row>
+    <row r="1139" spans="1:13">
+      <c r="A1139" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B1139">
+        <v>5744.07</v>
+      </c>
+      <c r="C1139">
+        <v>15.87</v>
+      </c>
+      <c r="D1139">
+        <v>5759.94</v>
+      </c>
+      <c r="E1139">
+        <v>244699</v>
+      </c>
+      <c r="F1139">
+        <v>1349</v>
+      </c>
+      <c r="G1139">
+        <v>246048</v>
+      </c>
+      <c r="H1139">
+        <v>265874</v>
+      </c>
+      <c r="I1139">
+        <v>0</v>
+      </c>
+      <c r="J1139">
+        <v>265874</v>
+      </c>
+      <c r="K1139">
+        <v>249910</v>
+      </c>
+      <c r="L1139">
+        <v>2983</v>
+      </c>
+      <c r="M1139">
+        <v>252893</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:13">
+      <c r="A1140" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B1140">
+        <v>5661.48</v>
+      </c>
+      <c r="C1140">
+        <v>7.00625</v>
+      </c>
+      <c r="D1140">
+        <v>5668.48625</v>
+      </c>
+      <c r="E1140">
+        <v>242883</v>
+      </c>
+      <c r="F1140">
+        <v>500</v>
+      </c>
+      <c r="G1140">
+        <v>243383</v>
+      </c>
+      <c r="H1140">
+        <v>258509</v>
+      </c>
+      <c r="I1140">
+        <v>0</v>
+      </c>
+      <c r="J1140">
+        <v>258509</v>
+      </c>
+      <c r="K1140">
+        <v>247673</v>
+      </c>
+      <c r="L1140">
+        <v>1341</v>
+      </c>
+      <c r="M1140">
+        <v>249014</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:13">
+      <c r="A1141" s="2">
+        <v>46170</v>
+      </c>
+      <c r="B1141">
+        <v>5629.66</v>
+      </c>
+      <c r="C1141">
+        <v>1.58828</v>
+      </c>
+      <c r="D1141">
+        <v>5631.24828</v>
+      </c>
+      <c r="E1141">
+        <v>232933</v>
+      </c>
+      <c r="F1141">
+        <v>0</v>
+      </c>
+      <c r="G1141">
+        <v>232933</v>
+      </c>
+      <c r="H1141">
+        <v>261479</v>
+      </c>
+      <c r="I1141">
+        <v>0</v>
+      </c>
+      <c r="J1141">
+        <v>261479</v>
+      </c>
+      <c r="K1141">
+        <v>242910</v>
+      </c>
+      <c r="L1141">
+        <v>1143</v>
+      </c>
+      <c r="M1141">
+        <v>244053</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:13">
+      <c r="A1142" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B1142">
+        <v>5245.58</v>
+      </c>
+      <c r="C1142">
+        <v>0</v>
+      </c>
+      <c r="D1142">
+        <v>5245.58</v>
+      </c>
+      <c r="E1142">
+        <v>226550</v>
+      </c>
+      <c r="F1142">
+        <v>0</v>
+      </c>
+      <c r="G1142">
+        <v>226550</v>
+      </c>
+      <c r="H1142">
+        <v>242988</v>
+      </c>
+      <c r="I1142">
+        <v>0</v>
+      </c>
+      <c r="J1142">
+        <v>242988</v>
+      </c>
+      <c r="K1142">
+        <v>228895</v>
+      </c>
+      <c r="L1142">
+        <v>0</v>
+      </c>
+      <c r="M1142">
+        <v>228895</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:13">
+      <c r="A1143" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B1143">
+        <v>5046.88</v>
+      </c>
+      <c r="C1143">
+        <v>0</v>
+      </c>
+      <c r="D1143">
+        <v>5046.88</v>
+      </c>
+      <c r="E1143">
+        <v>214236</v>
+      </c>
+      <c r="F1143">
+        <v>0</v>
+      </c>
+      <c r="G1143">
+        <v>214236</v>
+      </c>
+      <c r="H1143">
+        <v>225629</v>
+      </c>
+      <c r="I1143">
+        <v>0</v>
+      </c>
+      <c r="J1143">
+        <v>225629</v>
+      </c>
+      <c r="K1143">
+        <v>221943</v>
+      </c>
+      <c r="L1143">
+        <v>0</v>
+      </c>
+      <c r="M1143">
+        <v>221943</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:13">
+      <c r="A1144" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B1144">
+        <v>4879.65</v>
+      </c>
+      <c r="C1144">
+        <v>0.152</v>
+      </c>
+      <c r="D1144">
+        <v>4879.802</v>
+      </c>
+      <c r="E1144">
+        <v>211086</v>
+      </c>
+      <c r="F1144">
+        <v>227</v>
+      </c>
+      <c r="G1144">
+        <v>211313</v>
+      </c>
+      <c r="H1144">
+        <v>215476</v>
+      </c>
+      <c r="I1144">
+        <v>0</v>
+      </c>
+      <c r="J1144">
+        <v>215476</v>
+      </c>
+      <c r="K1144">
+        <v>223711</v>
+      </c>
+      <c r="L1144">
+        <v>0</v>
+      </c>
+      <c r="M1144">
+        <v>223711</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:13">
+      <c r="A1145" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B1145">
+        <v>5222.03</v>
+      </c>
+      <c r="C1145">
+        <v>0.36</v>
+      </c>
+      <c r="D1145">
+        <v>5222.389999999999</v>
+      </c>
+      <c r="E1145">
+        <v>226666</v>
+      </c>
+      <c r="F1145">
+        <v>0</v>
+      </c>
+      <c r="G1145">
+        <v>226666</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:13">
+      <c r="A1146" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B1146">
+        <v>5291.49</v>
+      </c>
+      <c r="C1146">
+        <v>3.071</v>
+      </c>
+      <c r="D1146">
+        <v>5294.561</v>
+      </c>
+      <c r="E1146">
+        <v>234212</v>
+      </c>
+      <c r="F1146">
+        <v>80</v>
+      </c>
+      <c r="G1146">
+        <v>234292</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:13">
+      <c r="A1147" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B1147">
+        <v>5495.55</v>
+      </c>
+      <c r="C1147">
+        <v>3.531</v>
+      </c>
+      <c r="D1147">
+        <v>5499.081</v>
+      </c>
+      <c r="E1147">
+        <v>239643</v>
+      </c>
+      <c r="F1147">
+        <v>0</v>
+      </c>
+      <c r="G1147">
+        <v>239643</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:13">
+      <c r="A1148" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B1148">
+        <v>5478.17</v>
+      </c>
+      <c r="C1148">
+        <v>0.05</v>
+      </c>
+      <c r="D1148">
+        <v>5478.22</v>
+      </c>
+      <c r="E1148">
+        <v>230429</v>
+      </c>
+      <c r="F1148">
+        <v>0</v>
+      </c>
+      <c r="G1148">
+        <v>230429</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:13">
+      <c r="A1149" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B1149">
+        <v>5381.77</v>
+      </c>
+      <c r="C1149">
+        <v>0.1773</v>
+      </c>
+      <c r="D1149">
+        <v>5381.947300000001</v>
+      </c>
+      <c r="E1149">
+        <v>231551</v>
+      </c>
+      <c r="F1149">
+        <v>0</v>
+      </c>
+      <c r="G1149">
+        <v>231551</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:13">
+      <c r="A1150" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B1150">
+        <v>5472.07</v>
+      </c>
+      <c r="C1150">
+        <v>1.3047</v>
+      </c>
+      <c r="D1150">
+        <v>5473.374699999999</v>
+      </c>
+      <c r="E1150">
+        <v>232788</v>
+      </c>
+      <c r="F1150">
+        <v>0</v>
+      </c>
+      <c r="G1150">
+        <v>232788</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:13">
+      <c r="A1151" s="2">
+        <v>46180</v>
+      </c>
+      <c r="B1151">
+        <v>5316.43</v>
+      </c>
+      <c r="C1151">
+        <v>0.03</v>
+      </c>
+      <c r="D1151">
+        <v>5316.46</v>
+      </c>
+      <c r="E1151">
+        <v>225129</v>
+      </c>
+      <c r="F1151">
+        <v>0</v>
+      </c>
+      <c r="G1151">
+        <v>225129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
